--- a/docs/downloads/04/tbl_homeland_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_avaradrano.xlsx
@@ -443,12 +443,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>23.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +460,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>14.3</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -511,12 +499,6 @@
         <is>
           <t>3</t>
         </is>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
